--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.58892197680794</v>
+        <v>4.80819982123129</v>
       </c>
       <c r="D2" t="n">
-        <v>29.19636713383504</v>
+        <v>4.744409659248194</v>
       </c>
       <c r="E2" t="n">
-        <v>2.007395037972489</v>
+        <v>0.3262016936705298</v>
       </c>
       <c r="F2" t="n">
-        <v>2.135587676738301</v>
+        <v>0.347032997469974</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.8558756044372</v>
+        <v>4.689079785721045</v>
       </c>
       <c r="D3" t="n">
-        <v>28.84680463714785</v>
+        <v>4.687605753536526</v>
       </c>
       <c r="E3" t="n">
-        <v>2.007395037972489</v>
+        <v>0.3262016936705298</v>
       </c>
       <c r="F3" t="n">
-        <v>2.135587676738301</v>
+        <v>0.347032997469974</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.20150860206105</v>
+        <v>5.232745147834921</v>
       </c>
       <c r="D4" t="n">
-        <v>32.43134405787522</v>
+        <v>5.270093409404723</v>
       </c>
       <c r="E4" t="n">
-        <v>2.007395037972489</v>
+        <v>0.3262016936705298</v>
       </c>
       <c r="F4" t="n">
-        <v>2.135587676738301</v>
+        <v>0.347032997469974</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.57618076693987</v>
+        <v>4.318629374627729</v>
       </c>
       <c r="D5" t="n">
-        <v>26.42885123009556</v>
+        <v>4.294688324890529</v>
       </c>
       <c r="E5" t="n">
-        <v>2.007395037972489</v>
+        <v>0.3262016936705298</v>
       </c>
       <c r="F5" t="n">
-        <v>2.135587676738301</v>
+        <v>0.347032997469974</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
